--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h0.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h0.xlsx
@@ -480,34 +480,34 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>0.4126</v>
       </c>
       <c r="F2">
-        <v>0.9939</v>
+        <v>1.1357</v>
       </c>
       <c r="G2">
-        <v>0.5814</v>
+        <v>0.7231</v>
       </c>
       <c r="H2">
-        <v>4.3035</v>
+        <v>7.1832</v>
       </c>
       <c r="I2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M2">
         <v>52</v>
@@ -524,37 +524,37 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.3691</v>
+        <v>0.404</v>
       </c>
       <c r="F3">
-        <v>0.8344</v>
+        <v>0.8248</v>
       </c>
       <c r="G3">
-        <v>0.4653</v>
+        <v>0.4208</v>
       </c>
       <c r="H3">
-        <v>2.7277</v>
+        <v>2.4811</v>
       </c>
       <c r="I3">
+        <v>26</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <v>23</v>
+      </c>
+      <c r="L3">
+        <v>12</v>
+      </c>
+      <c r="M3">
         <v>35</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>32</v>
-      </c>
-      <c r="L3">
-        <v>9</v>
-      </c>
-      <c r="M3">
-        <v>41</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -571,34 +571,34 @@
         <v>0</v>
       </c>
       <c r="D4">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>0.4302</v>
+      </c>
+      <c r="F4">
+        <v>1.7757</v>
+      </c>
+      <c r="G4">
+        <v>1.3455</v>
+      </c>
+      <c r="H4">
+        <v>16.8639</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
         <v>11</v>
       </c>
-      <c r="E4">
-        <v>0.5746</v>
-      </c>
-      <c r="F4">
-        <v>1.5885</v>
-      </c>
-      <c r="G4">
-        <v>1.0139</v>
-      </c>
-      <c r="H4">
-        <v>10.1768</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>8</v>
-      </c>
-      <c r="K4">
-        <v>8</v>
-      </c>
       <c r="L4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N4">
         <v>0</v>
